--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:01:27+00:00</t>
+    <t>2026-09-02T09:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:13:42+00:00</t>
+    <t>2026-09-02T09:46:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:46:11+00:00</t>
+    <t>2026-09-02T09:54:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:54:50+00:00</t>
+    <t>2026-09-02T10:49:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:49:18+00:00</t>
+    <t>2026-09-02T11:53:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T11:53:33+00:00</t>
+    <t>2026-09-02T12:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:13:25+00:00</t>
+    <t>2026-09-02T12:45:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:45:31+00:00</t>
+    <t>2026-09-02T21:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>NUM-DIZ</t>
+    <t>Medizininformatik Initiative</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>NUM-DIZ (https://www.netzwerk-universitaetsmedizin.de)</t>
+    <t>Medizininformatik Initiative (https://www.medizininformatik-initiative.de)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T21:03:23+00:00</t>
+    <t>2026-09-02T21:10:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T21:10:40+00:00</t>
+    <t>2026-09-02T21:48:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T21:48:21+00:00</t>
+    <t>2026-09-03T04:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T04:37:30+00:00</t>
+    <t>2026-09-03T05:02:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
